--- a/data/trans_bre/IP16A06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A06-Habitat-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 0,0</t>
+          <t>-11,16; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 7,69</t>
+          <t>-2,86; 7,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,96</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 0,0</t>
+          <t>-12,27; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 0,0</t>
+          <t>-6,56; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 1,58</t>
+          <t>-9,86; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 10,73</t>
+          <t>-3,61; 13,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 6,41</t>
+          <t>-6,94; 5,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 0,0</t>
+          <t>-8,86; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 2,04</t>
+          <t>-3,26; 2,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,44</t>
+          <t>-1,83; 2,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,84</t>
+          <t>-2,28; 0,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 314,5</t>
+          <t>-100,0; 267,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-86,44; 558,63</t>
+          <t>-83,14; 631,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A06-Habitat-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 0,0</t>
+          <t>-8,93; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 7,55</t>
+          <t>-2,66; 7,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 7,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 0,0</t>
+          <t>-13,8; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 0,0</t>
+          <t>-6,27; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 1,59</t>
+          <t>-10,0; 2,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 13,03</t>
+          <t>-3,59; 11,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 5,26</t>
+          <t>-6,61; 6,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 0,0</t>
+          <t>-7,18; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,13</t>
+          <t>-3,18; 2,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,34</t>
+          <t>-1,95; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,95</t>
+          <t>-2,96; 0,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 267,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-83,14; 631,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A06-Habitat-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 0,0</t>
+          <t>-10,31; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 7,7</t>
+          <t>-2,75; 7,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,8</t>
+          <t>0,0; 8,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,09</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 0,0</t>
+          <t>-13,51; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 0,0</t>
+          <t>-6,06; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 2,61</t>
+          <t>-9,51; 1,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 11,87</t>
+          <t>-3,66; 10,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 6,46</t>
+          <t>-6,74; 6,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 0,0</t>
+          <t>-9,5; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,25</t>
+          <t>-3,07; 2,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,55</t>
+          <t>-1,71; 2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,93</t>
+          <t>-2,63; 0,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 314,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,44; 558,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A06-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,131 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,93</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.3609957841136022</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-10,31; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.805502573369051</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>109,37%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,75; 7,69</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,96</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,34</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C7" s="5" t="n">
+        <v>0.3618666937339125</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6464838462617191</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2977956218180834</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1.294563438208552</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,89</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,21</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-58,84%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.2812550677381793</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-13,51; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,06; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-9,51; 1,58</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.671346302293734</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.180598731225943</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.500561448429671</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +735,211 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>70,74%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-22,83%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.9136850238907892</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.365697460216894</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.3923597347758596</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.5388249653630405</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,66; 10,73</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,74; 6,41</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-9,5; 0,0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.121262015746928</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.842709543386505</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.905942694785736</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6290880828599161</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.04091337617041918</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.2270043481370464</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.31386550994211</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.121399753725276</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2279908081540945</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.7350673120082857</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.674770810070487</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.570419535116119</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.173375747335365</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.238826756546164</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-26,98%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-44,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,07; 2,04</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,71; 2,44</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 0,84</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 314,5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-86,44; 558,63</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.1446715472338206</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.05966639748851568</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.08764357085712167</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.3253705150421489</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1681030155435559</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.3510836635274259</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.6648880059344379</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.4378711350428778</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.5044808826335896</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.354401540615768</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.6042486515369568</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.2525372458998866</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>2.262898164500206</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +948,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
